--- a/Data/quest_reference.xlsx
+++ b/Data/quest_reference.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -477,425 +477,365 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Animal Magnetism</t>
+          <t>The Ides of Milk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ernest the Chicken; Priest in Peril; The Restless Ghost</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Crafting 19 (ID:14); Prayer 31 (ID:13); Ranged 30 (ID:10); Slayer 18 (ID:19); Woodcutting 35 (ID:18)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>23.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Another Slice of H.A.M.</t>
+          <t>Learning the Ropes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Death to the Dorgeshuun; The Dig Site; The Giant Dwarf</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Attack 15 (ID:1); Prayer 25 (ID:13)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Ascent of Arceuus</t>
+          <t>Below Ice Mountain</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Client of Kourend</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hunter 12 (ID:22)</t>
+          <t>Quest point 16 (ID:23)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>At First Light</t>
+          <t>X Marks the Spot</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Children of the Sun; Eagles' Peak</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hunter 46 (ID:22); Herblore 30 (ID:8); Construction 27 (ID:21)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>17.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Below Ice Mountain</t>
+          <t>The Corsair Curse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Quest point 16 (ID:23)</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Between a Rock...</t>
+          <t>Misthalin Mystery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Dwarf Cannon; Fishing Contest</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Defence 30 (ID:7); Mining 40 (ID:3); Smithing 50 (ID:6)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Big Chompy Bird Hunting</t>
+          <t>Rune Mysteries</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Novice</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Cooking 30 (ID:12); Fletching 5 (ID:17); Ranged 30 (ID:10)</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>11.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Biohazard</t>
+          <t>Dragon Slayer I</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Plague City</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Quest point 32 (ID:23); Crafting 8 (ID:14)</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Black Knights' Fortress</t>
+          <t>Pirate's Treasure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Novice</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Quest point 12 (ID:23)</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bone Voyage</t>
+          <t>Goblin Diplomacy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The Dig Site</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kudos 100 (ID:24)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cabin Fever</t>
+          <t>The Knight's Sword</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Pirate's Treasure; Rum Deal</t>
-        </is>
-      </c>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Agility 42 (ID:5); Crafting 45 (ID:14); Smithing 50 (ID:6); Ranged 40 (ID:10)</t>
+          <t>Cooking 10 (ID:12); Mining 10 (ID:3); Mining 15 (ID:3); Smithing 15 (ID:6)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="I12" t="n">
-        <v>26.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Children of the Sun</t>
+          <t>Witch's Potion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -921,47 +861,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Client of Kourend</t>
+          <t>Black Knights' Fortress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>X Marks the Spot</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Quest point 12 (ID:23)</t>
+        </is>
+      </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clock Tower</t>
+          <t>Doric's Quest</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -970,79 +910,75 @@
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mining 15 (ID:3)</t>
+        </is>
+      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cold War</t>
+          <t>Prince Ali Rescue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Novice</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Agility 30 (ID:5); Construction 34 (ID:21); Crafting 30 (ID:14); Hunter 10 (ID:22); Thieving 15 (ID:11); Woodcutting 50 (ID:18)</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>24.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Contact!</t>
+          <t>Imp Catcher</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Prince Ali Rescue; Icthlarin's Little Helper</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1051,23 +987,23 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cook's Assistant</t>
+          <t>Vampyre Slayer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1082,23 +1018,23 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Corsair Curse</t>
+          <t>Ernest the Chicken</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Novice</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1113,174 +1049,142 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Creature of Fenkenstrain</t>
+          <t>The Restless Ghost</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Priest in Peril; The Restless Ghost</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Crafting 20 (ID:14); Smithing 4 (ID:6); Thieving 25 (ID:11)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>11.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Curse of Arrav</t>
+          <t>Sheep Shearer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Defender of Varrock; Troll Romance</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mining 64 (ID:3); Ranged 62 (ID:10); Thieving 62 (ID:11); Agility 61 (ID:5); Strength 58 (ID:4); Slayer 37 (ID:19)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>46.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Darkness of Hallowvale</t>
+          <t>Shield of Arrav</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>In Aid of the Myreque</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Agility 26 (ID:5); Construction 5 (ID:21); Crafting 32 (ID:14); Magic 33 (ID:16); Mining 20 (ID:3); Strength 40 (ID:4); Thieving 22 (ID:11)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>28.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Death on the Isle</t>
+          <t>Demon Slayer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Children of the Sun</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Agility 32 (ID:5); Thieving 34 (ID:11)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>11.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Death Plateau</t>
+          <t>Romeo &amp; Juliet</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1306,121 +1210,109 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Death to the Dorgeshuun</t>
+          <t>Cook's Assistant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>The Lost Tribe</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Agility 23 (ID:5); Thieving 23 (ID:11)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>9.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Defender of Varrock</t>
+          <t>Druidic Ritual</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Shield of Arrav; Temple of Ikov; Below Ice Mountain; Family Crest; Garden of Tranquillity; What Lies Below; Romeo &amp; Juliet; Demon Slayer</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Smithing 55 (ID:6); Hunter 52 (ID:22)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>23.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Demon Slayer</t>
+          <t>Lost City</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Crafting 31 (ID:14); Woodcutting 36 (ID:18)</t>
+        </is>
+      </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Depths of Despair</t>
+          <t>Witch's House</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1428,194 +1320,174 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Client of Kourend</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Agility 18 (ID:5)</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Desert Treasure I</t>
+          <t>Merlin's Crystal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>The Dig Site; Temple of Ikov; The Tourist Trap; Troll Stronghold; Priest in Peril; Waterfall Quest</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Firemaking 50 (ID:15); Magic 50 (ID:16); Slayer 10 (ID:19); Thieving 53 (ID:11)</t>
-        </is>
-      </c>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>30.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Desert Treasure II - The Fallen Empire</t>
+          <t>Heroes' Quest</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Grandmaster</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Desert Treasure I; Secrets of the North; Enakhra's Lament; Temple of the Eye; The Garden of Death; Below Ice Mountain; His Faithful Servants</t>
+          <t>Dragon Slayer I; Druidic Ritual; Lost City; Merlin's Crystal; Shield of Arrav</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Firemaking 75 (ID:15); Magic 75 (ID:16); Herblore 62 (ID:8); Thieving 70 (ID:11); Runecraft 60 (ID:18); Construction 60 (ID:21)</t>
+          <t>Quest point 55 (ID:23); Cooking 53 (ID:12); Fishing 53 (ID:9); Herblore 25 (ID:8); Mining 50 (ID:3)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>402</v>
+        <v>236</v>
       </c>
       <c r="I30" t="n">
-        <v>58.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Devious Minds</t>
+          <t>Scorpion Catcher</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Doric's Quest; Enter the Abyss; Troll Stronghold; Wanted!</t>
+          <t>Alfred Grimhand's Barcrawl</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fletching 50 (ID:17); Runecraft 50 (ID:18); Smithing 65 (ID:6)</t>
+          <t>Prayer 31 (ID:13)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="I31" t="n">
-        <v>26.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Dig Site</t>
+          <t>Family Crest</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Druidic Ritual</t>
-        </is>
-      </c>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Agility 10 (ID:5); Herblore 10 (ID:8); Thieving 25 (ID:11)</t>
+          <t>Crafting 40 (ID:14); Magic 59 (ID:16); Mining 40 (ID:3); Smithing 40 (ID:6)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="I32" t="n">
-        <v>10.5</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Doric's Quest</t>
+          <t>Fishing Contest</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1626,7 +1498,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mining 15 (ID:3)</t>
+          <t>Fishing 10 (ID:9)</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1636,134 +1508,122 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dragon Slayer I</t>
+          <t>Tribal Totem</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Quest point 32 (ID:23); Crafting 8 (ID:14)</t>
+          <t>Thieving 21 (ID:11)</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="I34" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dragon Slayer II</t>
+          <t>Monk's Friend</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Grandmaster</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Animal Magnetism; Barbarian Firemaking; Bone Voyage; Client of Kourend; Dream Mentor; Ghosts Ahoy; Legends' Quest; A Tail of Two Cats</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Quest point 200 (ID:23); Agility 60 (ID:5); Construction 50 (ID:21); Crafting 62 (ID:14); Hitpoints 50 (ID:2); Magic 75 (ID:16); Mining 68 (ID:3); Smithing 70 (ID:6); Thieving 60 (ID:11)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>91.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dream Mentor</t>
+          <t>Temple of Ikov</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Eadgar's Ruse; Lunar Diplomacy</t>
-        </is>
-      </c>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Combat 85 (ID:25)</t>
+          <t>Ranged 40 (ID:10); Thieving 42 (ID:11)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I36" t="n">
-        <v>15.5</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Druidic Ritual</t>
+          <t>Clock Tower</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1789,43 +1649,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dwarf Cannon</t>
+          <t>Holy Grail</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Merlin's Crystal</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Attack 20 (ID:1)</t>
+        </is>
+      </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eadgar's Ruse</t>
+          <t>Tree Gnome Village</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1833,73 +1701,61 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Druidic Ritual; Troll Stronghold</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Herblore 31 (ID:8)</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eagles' Peak</t>
+          <t>Fight Arena</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Hunter 27 (ID:22)</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Elemental Workshop I</t>
+          <t>Hazeel Cult</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1908,107 +1764,91 @@
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Crafting 20 (ID:14); Mining 20 (ID:3); Mining 30 (ID:3); Smithing 20 (ID:6)</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Elemental Workshop II</t>
+          <t>Sheep Herder</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Elemental Workshop I</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Magic 20 (ID:16); Smithing 30 (ID:6)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Enakhra's Lament</t>
+          <t>Plague City</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Crafting 50 (ID:14); Firemaking 45 (ID:15); Magic 39 (ID:16); Mining 45 (ID:3); Prayer 43 (ID:13)</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>30.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Enlightened Journey</t>
+          <t>Sea Slug</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2019,36 +1859,36 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quest point 20 (ID:23); Firemaking 20 (ID:15); Farming 30 (ID:20); Crafting 36 (ID:14)</t>
+          <t>Firemaking 30 (ID:15)</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="I44" t="n">
-        <v>16.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ernest the Chicken</t>
+          <t>Waterfall Quest</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2063,18 +1903,18 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ethically Acquired Antiquities</t>
+          <t>Jungle Potion</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2084,36 +1924,36 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Children of the Sun; Shield of Arrav</t>
+          <t>Druidic Ritual</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Thieving 25 (ID:11)</t>
+          <t>Herblore 3 (ID:8)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Eyes of Glouphrie</t>
+          <t>The Grand Tree</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2121,147 +1961,139 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>The Grand Tree</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Construction 5 (ID:21); Magic 46 (ID:16); Runecraft 13 (ID:18)</t>
+          <t>Agility 25 (ID:5)</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="I47" t="n">
-        <v>12.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fairytale I - Growing Pains</t>
+          <t>Underground Pass</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lost City; Nature Spirit</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>Biohazard</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ranged 25 (ID:10)</t>
+        </is>
+      </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fairytale II - Cure a Queen</t>
+          <t>Observatory Quest</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Druidic Ritual; Fairytale I - Growing Pains</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Farming 49 (ID:20); Herblore 57 (ID:8); Thieving 40 (ID:11)</t>
-        </is>
-      </c>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>22.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Family Crest</t>
+          <t>The Tourist Trap</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crafting 40 (ID:14); Magic 59 (ID:16); Mining 40 (ID:3); Smithing 40 (ID:6)</t>
+          <t>Fletching 10 (ID:17); Smithing 20 (ID:6)</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="I50" t="n">
-        <v>24.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Feud</t>
+          <t>Watchtower</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2269,39 +2101,43 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Druidic Ritual</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Thieving 30 (ID:11)</t>
+          <t>Agility 25 (ID:5); Herblore 14 (ID:8); Magic 15 (ID:16); Mining 40 (ID:3); Thieving 15 (ID:11)</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fight Arena</t>
+          <t>Dwarf Cannon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Novice</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2316,18 +2152,18 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fishing Contest</t>
+          <t>Murder Mystery</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2336,33 +2172,29 @@
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Fishing 10 (ID:9)</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Forgettable Tale...</t>
+          <t>The Dig Site</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2372,51 +2204,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>The Giant Dwarf; Fishing Contest</t>
+          <t>Druidic Ritual</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cooking 22 (ID:12); Farming 17 (ID:20)</t>
+          <t>Agility 10 (ID:5); Herblore 10 (ID:8); Thieving 25 (ID:11)</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I54" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Forsaken Tower</t>
+          <t>Gertrude's Cat</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Client of Kourend</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2425,18 +2253,18 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Fremennik Exiles</t>
+          <t>Legends' Quest</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2446,75 +2274,67 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>The Fremennik Isles; Lunar Diplomacy; Mountain Daughter; Heroes' Quest</t>
+          <t>Family Crest; Heroes' Quest; Shilo Village; Underground Pass; Waterfall Quest</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crafting 65 (ID:14); Fishing 60 (ID:9); Runecraft 55 (ID:18); Slayer 60 (ID:19); Smithing 60 (ID:6)</t>
+          <t>Quest point 107 (ID:23); Agility 50 (ID:5); Crafting 50 (ID:14); Herblore 45 (ID:8); Magic 56 (ID:16); Mining 52 (ID:3); Prayer 42 (ID:13); Smithing 50 (ID:6); Strength 50 (ID:4); Thieving 50 (ID:11); Woodcutting 50 (ID:18)</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H56" t="n">
-        <v>300</v>
+        <v>602</v>
       </c>
       <c r="I56" t="n">
-        <v>43</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Fremennik Isles</t>
+          <t>Death Plateau</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>The Fremennik Trials</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Construction 20 (ID:21); Crafting 46 (ID:14); Woodcutting 56 (ID:18)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>19.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Fremennik Trials</t>
+          <t>Eadgar's Ruse</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2522,30 +2342,38 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Druidic Ritual; Troll Stronghold</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Herblore 31 (ID:8)</t>
+        </is>
+      </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Garden of Death</t>
+          <t>Big Chompy Bird Hunting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2556,175 +2384,175 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Farming 20 (ID:20)</t>
+          <t>Cooking 30 (ID:12); Fletching 5 (ID:17); Ranged 30 (ID:10)</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Garden of Tranquillity</t>
+          <t>Elemental Workshop I</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Creature of Fenkenstrain</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Farming 25 (ID:20)</t>
+          <t>Crafting 20 (ID:14); Mining 20 (ID:3); Mining 30 (ID:3); Smithing 20 (ID:6)</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H60" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="I60" t="n">
-        <v>6.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gertrude's Cat</t>
+          <t>Nature Spirit</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Priest in Peril; The Restless Ghost</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Crafting 18 (ID:14)</t>
+        </is>
+      </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Getting Ahead</t>
+          <t>Priest in Peril</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Novice</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Construction 26 (ID:21); Crafting 30 (ID:14)</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>9.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ghosts Ahoy</t>
+          <t>Regicide</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Priest in Peril; The Restless Ghost</t>
+          <t>Underground Pass</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Agility 25 (ID:5); Cooking 20 (ID:12)</t>
+          <t>Agility 56 (ID:5); Crafting 10 (ID:14)</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="I63" t="n">
-        <v>10.5</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Giant Dwarf</t>
+          <t>Tai Bwo Wannai Trio</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2732,65 +2560,77 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jungle Potion</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crafting 12 (ID:14); Firemaking 16 (ID:15); Magic 33 (ID:16); Thieving 14 (ID:11)</t>
+          <t>Agility 15 (ID:5); Cooking 30 (ID:12); Fishing 5 (ID:9); Fishing 65 (ID:9); Herblore 34 (ID:8)</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H64" t="n">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="I64" t="n">
-        <v>13.5</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Goblin Diplomacy</t>
+          <t>Troll Stronghold</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Death Plateau</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Agility 15 (ID:5)</t>
+        </is>
+      </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Golem</t>
+          <t>Shades of Mort'ton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2798,34 +2638,38 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Druidic Ritual; Priest in Peril</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Crafting 20 (ID:14); Thieving 25 (ID:11)</t>
+          <t>Crafting 20 (ID:14); Firemaking 5 (ID:15); Herblore 15 (ID:8)</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I66" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Grand Tree</t>
+          <t>The Fremennik Trials</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2834,135 +2678,127 @@
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Agility 25 (ID:5)</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Great Brain Robbery</t>
+          <t>Horror from the Deep</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cabin Fever; Creature of Fenkenstrain; Recipe for Disaster/Freeing Pirate Pete</t>
+          <t>Alfred Grimhand's Barcrawl</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Crafting 16 (ID:14); Construction 30 (ID:21); Prayer 50 (ID:13)</t>
+          <t>Agility 35 (ID:5)</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="I68" t="n">
-        <v>18.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Grim Tales</t>
+          <t>Throne of Miscellania</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Druidic Ritual; Witch's House</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Agility 59 (ID:5); Farming 45 (ID:20); Herblore 52 (ID:8); Thieving 58 (ID:11); Woodcutting 71 (ID:18)</t>
-        </is>
-      </c>
+          <t>The Fremennik Trials; Heroes' Quest</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
         <v>2</v>
       </c>
       <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>5</v>
-      </c>
-      <c r="H69" t="n">
-        <v>285</v>
-      </c>
-      <c r="I69" t="n">
-        <v>39.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Hand in the Sand</t>
+          <t>Monkey Madness I</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Crafting 49 (ID:14); Thieving 17 (ID:11)</t>
-        </is>
-      </c>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>The Grand Tree; Tree Gnome Village</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>10.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -3007,160 +2843,168 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hazeel Cult</t>
+          <t>Troll Romance</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Troll Stronghold</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Agility 28 (ID:5); Woodcutting 45 (ID:18)</t>
+        </is>
+      </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Heart of Darkness</t>
+          <t>In Search of the Myreque</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Twilight's Promise</t>
+          <t>Nature Spirit</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mining 55 (ID:3); Thieving 48 (ID:11); Slayer 48 (ID:19); Agility 46 (ID:5)</t>
+          <t>Agility 25 (ID:5)</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="I73" t="n">
-        <v>27.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Heroes' Quest</t>
+          <t>Creature of Fenkenstrain</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Dragon Slayer I; Druidic Ritual; Lost City; Merlin's Crystal; Shield of Arrav</t>
+          <t>Priest in Peril; The Restless Ghost</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Quest point 55 (ID:23); Cooking 53 (ID:12); Fishing 53 (ID:9); Herblore 25 (ID:8); Mining 50 (ID:3)</t>
+          <t>Crafting 20 (ID:14); Smithing 4 (ID:6); Thieving 25 (ID:11)</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
-        <v>236</v>
+        <v>49</v>
       </c>
       <c r="I74" t="n">
-        <v>36.6</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Holy Grail</t>
+          <t>Roving Elves</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Merlin's Crystal</t>
+          <t>Regicide; Waterfall Quest</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Attack 20 (ID:1)</t>
+          <t>Agility 56 (ID:5)</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Horror from the Deep</t>
+          <t>Ghosts Ahoy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3170,141 +3014,149 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Alfred Grimhand's Barcrawl</t>
+          <t>Priest in Peril; The Restless Ghost</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Agility 35 (ID:5)</t>
+          <t>Agility 25 (ID:5); Cooking 20 (ID:12)</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I76" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Icthlarin's Little Helper</t>
+          <t>One Small Favour</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Gertrude's Cat</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>Rune Mysteries; Shilo Village</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Agility 36 (ID:5); Crafting 25 (ID:14); Herblore 18 (ID:8); Smithing 30 (ID:6)</t>
+        </is>
+      </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Imp Catcher</t>
+          <t>Mountain Daughter</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Agility 20 (ID:5)</t>
+        </is>
+      </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>In Aid of the Myreque</t>
+          <t>Between a Rock...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>In Search of the Myreque</t>
+          <t>Dwarf Cannon; Fishing Contest</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Agility 25 (ID:5); Crafting 25 (ID:14); Fishing 16 (ID:9); Magic 7 (ID:16); Mining 15 (ID:3); Smithing 50 (ID:6)</t>
+          <t>Defence 30 (ID:7); Mining 40 (ID:3); Smithing 50 (ID:6)</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="I79" t="n">
-        <v>22.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>In Search of the Myreque</t>
+          <t>The Feud</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3312,155 +3164,143 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Nature Spirit</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Agility 25 (ID:5)</t>
+          <t>Thieving 30 (ID:11)</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I80" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jungle Potion</t>
+          <t>The Golem</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Druidic Ritual</t>
-        </is>
-      </c>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Herblore 3 (ID:8)</t>
+          <t>Crafting 20 (ID:14); Thieving 25 (ID:11)</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>King's Ransom</t>
+          <t>Desert Treasure I</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Black Knights' Fortress; Holy Grail; Murder Mystery; One Small Favour</t>
+          <t>The Dig Site; Temple of Ikov; The Tourist Trap; Troll Stronghold; Priest in Peril; Waterfall Quest</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Defence 65 (ID:7); Magic 45 (ID:16)</t>
+          <t>Firemaking 50 (ID:15); Magic 50 (ID:16); Slayer 10 (ID:19); Thieving 53 (ID:11)</t>
         </is>
       </c>
       <c r="F82" t="n">
+        <v>6</v>
+      </c>
+      <c r="G82" t="n">
         <v>4</v>
       </c>
-      <c r="G82" t="n">
-        <v>2</v>
-      </c>
       <c r="H82" t="n">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A Kingdom Divided</t>
+          <t>Icthlarin's Little Helper</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Architectural Alliance; The Ascent of Arceuus; The Depths of Despair; Druidic Ritual; The Forsaken Tower; The Queen of Thieves; Tale of the Righteous</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Agility 54 (ID:5); Crafting 38 (ID:14); Herblore 50 (ID:8); Magic 35 (ID:16); Mining 42 (ID:3); Thieving 52 (ID:11); Woodcutting 52 (ID:18)</t>
-        </is>
-      </c>
+          <t>Gertrude's Cat</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>49.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Knight's Sword</t>
+          <t>Tears of Guthix</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3471,7 +3311,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cooking 10 (ID:12); Mining 10 (ID:3); Mining 15 (ID:3); Smithing 15 (ID:6)</t>
+          <t>Quest point 43 (ID:23); Crafting 20 (ID:14); Firemaking 49 (ID:15); Mining 20 (ID:3)</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -3481,60 +3321,60 @@
         <v>4</v>
       </c>
       <c r="H84" t="n">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="I84" t="n">
-        <v>11</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Legends' Quest</t>
+          <t>The Lost Tribe</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Family Crest; Heroes' Quest; Shilo Village; Underground Pass; Waterfall Quest</t>
+          <t>Goblin Diplomacy; Rune Mysteries</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Quest point 107 (ID:23); Agility 50 (ID:5); Crafting 50 (ID:14); Herblore 45 (ID:8); Magic 56 (ID:16); Mining 52 (ID:3); Prayer 42 (ID:13); Smithing 50 (ID:6); Strength 50 (ID:4); Thieving 50 (ID:11); Woodcutting 50 (ID:18)</t>
+          <t>Agility 13 (ID:5); Mining 17 (ID:3); Thieving 13 (ID:11)</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G85" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
-        <v>602</v>
+        <v>43</v>
       </c>
       <c r="I85" t="n">
-        <v>80.2</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lost City</t>
+          <t>The Giant Dwarf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3545,148 +3385,144 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Crafting 31 (ID:14); Woodcutting 36 (ID:18)</t>
+          <t>Crafting 12 (ID:14); Firemaking 16 (ID:15); Magic 33 (ID:16); Thieving 14 (ID:11)</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H86" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I86" t="n">
-        <v>10.7</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Lost Tribe</t>
+          <t>Recruitment Drive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Novice</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Goblin Diplomacy; Rune Mysteries</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Agility 13 (ID:5); Mining 17 (ID:3); Thieving 13 (ID:11)</t>
-        </is>
-      </c>
+          <t>Black Knights' Fortress; Druidic Ritual</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
         <v>2</v>
       </c>
       <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>3</v>
-      </c>
-      <c r="H87" t="n">
-        <v>43</v>
-      </c>
-      <c r="I87" t="n">
-        <v>11.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lunar Diplomacy</t>
+          <t>Mourning's End Part I</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The Fremennik Trials; Lost City; Rune Mysteries; Shilo Village</t>
+          <t>Big Chompy Bird Hunting; Roving Elves; Sheep Herder</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Crafting 61 (ID:14); Defence 40 (ID:7); Firemaking 49 (ID:15); Herblore 5 (ID:8); Magic 65 (ID:16); Mining 60 (ID:3); Woodcutting 55 (ID:18)</t>
+          <t>Ranged 60 (ID:10); Thieving 50 (ID:11)</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
-        <v>335</v>
+        <v>110</v>
       </c>
       <c r="I88" t="n">
-        <v>47.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Making Friends with My Arm</t>
+          <t>Forgettable Tale...</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cold War; My Arm's Big Adventure; Romeo &amp; Juliet; Swan Song</t>
+          <t>The Giant Dwarf; Fishing Contest</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Agility 68 (ID:5); Construction 35 (ID:21); Firemaking 66 (ID:15); Mining 72 (ID:3)</t>
+          <t>Cooking 22 (ID:12); Farming 17 (ID:20)</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
-        <v>241</v>
+        <v>39</v>
       </c>
       <c r="I89" t="n">
-        <v>36.1</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Making History</t>
+          <t>Garden of Tranquillity</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3696,42 +3532,46 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Priest in Peril; The Restless Ghost</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>Creature of Fenkenstrain</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Farming 25 (ID:20)</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Meat and Greet</t>
+          <t>A Tail of Two Cats</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Children of the Sun</t>
+          <t>Icthlarin's Little Helper</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3745,18 +3585,18 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Merlin's Crystal</t>
+          <t>Wanted!</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3764,41 +3604,53 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>The Lost Tribe; Priest in Peril; Recruitment Drive; Started:Enter the Abyss</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Quest point 32 (ID:23)</t>
+        </is>
+      </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Misthalin Mystery</t>
+          <t>Mourning's End Part II</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Mourning's End Part I</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3807,123 +3659,131 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Monk's Friend</t>
+          <t>Rum Deal</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Priest in Peril; Zogre Flesh Eaters</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Crafting 42 (ID:14); Farming 40 (ID:20); Fishing 50 (ID:9); Prayer 47 (ID:13); Slayer 42 (ID:19)</t>
+        </is>
+      </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Monkey Madness I</t>
+          <t>Shadow of the Storm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>The Grand Tree; Tree Gnome Village</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>Demon Slayer; The Golem</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Crafting 30 (ID:14)</t>
+        </is>
+      </c>
       <c r="F95" t="n">
         <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Monkey Madness II</t>
+          <t>Making History</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Grandmaster</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Enlightened Journey; The Eyes of Glouphrie; Recipe for Disaster/Freeing King Awowogei; Troll Stronghold; Watchtower</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Agility 55 (ID:5); Crafting 70 (ID:14); Firemaking 60 (ID:15); Hunter 60 (ID:22); Slayer 69 (ID:19); Thieving 55 (ID:11)</t>
-        </is>
-      </c>
+          <t>Priest in Peril; The Restless Ghost</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>52.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mountain Daughter</t>
+          <t>Ratcatchers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3931,139 +3791,143 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Agility 20 (ID:5)</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Icthlarin's Little Helper; Started:The Giant Dwarf</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mourning's End Part I</t>
+          <t>Spirits of the Elid</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Big Chompy Bird Hunting; Roving Elves; Sheep Herder</t>
-        </is>
-      </c>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ranged 60 (ID:10); Thieving 50 (ID:11)</t>
+          <t>Magic 33 (ID:16); Mining 37 (ID:3); Ranged 37 (ID:10); Thieving 37 (ID:11)</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H98" t="n">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="I98" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mourning's End Part II</t>
+          <t>Devious Minds</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mourning's End Part I</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>Doric's Quest; Enter the Abyss; Troll Stronghold; Wanted!</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Fletching 50 (ID:17); Runecraft 50 (ID:26); Smithing 65 (ID:6)</t>
+        </is>
+      </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Murder Mystery</t>
+          <t>The Hand in the Sand</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Crafting 49 (ID:14); Thieving 17 (ID:11)</t>
+        </is>
+      </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>My Arm's Big Adventure</t>
+          <t>Enakhra's Lament</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4071,92 +3935,88 @@
           <t>Experienced</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Eadgar's Ruse; The Feud; Jungle Potion</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Farming 29 (ID:20); Woodcutting 10 (ID:18)</t>
+          <t>Crafting 50 (ID:14); Firemaking 45 (ID:15); Magic 39 (ID:16); Mining 45 (ID:3); Prayer 43 (ID:13)</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H101" t="n">
-        <v>39</v>
+        <v>222</v>
       </c>
       <c r="I101" t="n">
-        <v>11.9</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nature Spirit</t>
+          <t>Cabin Fever</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Priest in Peril; The Restless Ghost</t>
+          <t>Pirate's Treasure; Rum Deal</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Crafting 18 (ID:14)</t>
+          <t>Agility 42 (ID:5); Crafting 45 (ID:14); Smithing 50 (ID:6); Ranged 40 (ID:10)</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>2</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H102" t="n">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="I102" t="n">
-        <v>6.8</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A Night at the Theatre</t>
+          <t>Fairytale I - Growing Pains</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>A Taste of Hope</t>
+          <t>Lost City; Nature Spirit</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4165,29 +4025,33 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Observatory Quest</t>
+          <t>Recipe for Disaster</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Recipe for Disaster/Defeating the Culinaromancer</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4196,18 +4060,18 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Olaf's Quest</t>
+          <t>In Aid of the Myreque</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4217,114 +4081,98 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>The Fremennik Trials</t>
+          <t>In Search of the Myreque</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Firemaking 40 (ID:15); Woodcutting 50 (ID:18)</t>
+          <t>Agility 25 (ID:5); Crafting 25 (ID:14); Fishing 16 (ID:9); Magic 7 (ID:16); Mining 15 (ID:3); Smithing 50 (ID:6)</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H105" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="I105" t="n">
-        <v>14</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>One Small Favour</t>
+          <t>A Soul's Bane</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Rune Mysteries; Shilo Village</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Agility 36 (ID:5); Crafting 25 (ID:14); Herblore 18 (ID:8); Smithing 30 (ID:6)</t>
-        </is>
-      </c>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>19.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>The Path of Glouphrie</t>
+          <t>Rag and Bone Man I</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>The Eyes of Glouphrie; Waterfall Quest; Tree Gnome Village</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Strength 60 (ID:4); Slayer 56 (ID:19); Thieving 56 (ID:11); Ranged 47 (ID:10); Agility 45 (ID:5)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>37.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Perilous Moons</t>
+          <t>Swan Song</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4334,454 +4182,506 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Twilight's Promise</t>
+          <t>Garden of Tranquillity; One Small Favour</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Slayer 48 (ID:19); Hunter 20 (ID:22); Fishing 20 (ID:9); Runecraft 20 (ID:18); Construction 10 (ID:21)</t>
+          <t>Quest point 100 (ID:23); Cooking 62 (ID:12); Crafting 40 (ID:14); Firemaking 42 (ID:15); Fishing 62 (ID:9); Magic 66 (ID:16); Smithing 45 (ID:6)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G108" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H108" t="n">
-        <v>118</v>
+        <v>417</v>
       </c>
       <c r="I108" t="n">
-        <v>21.8</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Pirate's Treasure</t>
+          <t>Royal Trouble</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Throne of Miscellania</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Agility 40 (ID:5); Slayer 40 (ID:19)</t>
+        </is>
+      </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Plague City</t>
+          <t>Death to the Dorgeshuun</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>The Lost Tribe</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Agility 23 (ID:5); Thieving 23 (ID:11)</t>
+        </is>
+      </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A Porcine of Interest</t>
+          <t>Fairytale II - Cure a Queen</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Druidic Ritual; Fairytale I - Growing Pains</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Farming 49 (ID:20); Herblore 57 (ID:8); Thieving 40 (ID:11)</t>
+        </is>
+      </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Priest in Peril</t>
+          <t>Lunar Diplomacy</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>The Fremennik Trials; Lost City; Rune Mysteries; Shilo Village</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Crafting 61 (ID:14); Defence 40 (ID:7); Firemaking 49 (ID:15); Herblore 5 (ID:8); Magic 65 (ID:16); Mining 60 (ID:3); Woodcutting 55 (ID:18)</t>
+        </is>
+      </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Prince Ali Rescue</t>
+          <t>The Eyes of Glouphrie</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>The Grand Tree</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Construction 5 (ID:21); Magic 46 (ID:16); Runecraft 13 (ID:26)</t>
+        </is>
+      </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The Queen of Thieves</t>
+          <t>Darkness of Hallowvale</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Client of Kourend</t>
+          <t>In Aid of the Myreque</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Thieving 20 (ID:11)</t>
+          <t>Agility 26 (ID:5); Construction 5 (ID:21); Crafting 32 (ID:14); Magic 33 (ID:16); Mining 20 (ID:3); Strength 40 (ID:4); Thieving 22 (ID:11)</t>
         </is>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H114" t="n">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="I114" t="n">
-        <v>6</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rag and Bone Man I</t>
+          <t>The Slug Menace</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Sea Slug; Wanted!</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Crafting 30 (ID:14); Runecraft 30 (ID:26); Slayer 30 (ID:19); Thieving 30 (ID:11)</t>
+        </is>
+      </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Rag and Bone Man II</t>
+          <t>Elemental Workshop II</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>The Fremennik Trials; Horror from the Deep; Rag and Bone Man I; Skippy and the Mogres; Started:Creature of Fenkenstrain; Started:Waterfall Quest; Started:Zogre Flesh Eaters</t>
+          <t>Elemental Workshop I</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Defence 20 (ID:7); Slayer 40 (ID:19)</t>
+          <t>Magic 20 (ID:16); Smithing 30 (ID:6)</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
         <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I116" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ratcatchers</t>
+          <t>My Arm's Big Adventure</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Icthlarin's Little Helper; Started:The Giant Dwarf</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>Eadgar's Ruse; The Feud; Jungle Potion</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Farming 29 (ID:20); Woodcutting 10 (ID:18)</t>
+        </is>
+      </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Recipe for Disaster</t>
+          <t>Enlightened Journey</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Recipe for Disaster/Defeating the Culinaromancer</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Quest point 20 (ID:23); Firemaking 20 (ID:15); Farming 30 (ID:20); Crafting 36 (ID:14)</t>
+        </is>
+      </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>100.1</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Another Cook's Quest</t>
+          <t>Eagles' Peak</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Cook's Assistant</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cooking 10 (ID:12)</t>
+          <t>Hunter 27 (ID:22)</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I119" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Freeing the Mountain Dwarf</t>
+          <t>Animal Magnetism</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Fishing Contest; Recipe for Disaster/Another Cook's Quest</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>Ernest the Chicken; Priest in Peril; The Restless Ghost</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Crafting 19 (ID:14); Prayer 31 (ID:13); Ranged 30 (ID:10); Slayer 18 (ID:19); Woodcutting 35 (ID:18)</t>
+        </is>
+      </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>100.3</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Freeing the Goblin generals</t>
+          <t>Contact!</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Goblin Diplomacy; Recipe for Disaster/Another Cook's Quest</t>
+          <t>Prince Ali Rescue; Icthlarin's Little Helper</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4801,320 +4701,320 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Freeing Pirate Pete</t>
+          <t>Cold War</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Recipe for Disaster/Another Cook's Quest</t>
-        </is>
-      </c>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cooking 31 (ID:12); Crafting 42 (ID:14); Smithing 31 (ID:6)</t>
+          <t>Agility 30 (ID:5); Construction 34 (ID:21); Crafting 30 (ID:14); Hunter 10 (ID:22); Thieving 15 (ID:11); Woodcutting 50 (ID:18)</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H122" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="I122" t="n">
-        <v>17.4</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Freeing the Lumbridge Guide</t>
+          <t>The Fremennik Isles</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Big Chompy Bird Hunting; Biohazard; Demon Slayer; Murder Mystery; Nature Spirit; Recipe for Disaster/Another Cook's Quest; Witch's House</t>
+          <t>The Fremennik Trials</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cooking 40 (ID:12)</t>
+          <t>Construction 20 (ID:21); Crafting 46 (ID:14); Woodcutting 56 (ID:18)</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H123" t="n">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="I123" t="n">
-        <v>15</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>100.6</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Freeing Evil Dave</t>
+          <t>The Great Brain Robbery</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Gertrude's Cat; Recipe for Disaster/Another Cook's Quest; Shadow of the Storm</t>
+          <t>Cabin Fever; Creature of Fenkenstrain; Recipe for Disaster/Freeing Pirate Pete</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cooking 25 (ID:12)</t>
+          <t>Crafting 16 (ID:14); Construction 30 (ID:21); Prayer 50 (ID:13)</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>3</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H124" t="n">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="I124" t="n">
-        <v>9.5</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>100.9</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Freeing Skrach Uglogwee</t>
+          <t>What Lies Below</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Big Chompy Bird Hunting; Recipe for Disaster/Another Cook's Quest</t>
+          <t>Rune Mysteries</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cooking 41 (ID:12); Firemaking 20 (ID:15)</t>
+          <t>Runecraft 35 (ID:26)</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="I125" t="n">
-        <v>13.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>100.8</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Freeing Sir Amik Varze</t>
+          <t>Olaf's Quest</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Another Cook's Quest; Started:Legends' Quest</t>
+          <t>The Fremennik Trials</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Farming 20 (ID:20)</t>
+          <t>Firemaking 40 (ID:15); Woodcutting 50 (ID:18)</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H126" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I126" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Freeing King Awowogei</t>
+          <t>Another Slice of H.A.M.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Monkey Madness I; Recipe for Disaster/Another Cook's Quest</t>
+          <t>Death to the Dorgeshuun; The Dig Site; The Giant Dwarf</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Agility 48 (ID:5); Cooking 70 (ID:12)</t>
+          <t>Attack 15 (ID:1); Prayer 25 (ID:13)</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G127" t="n">
         <v>2</v>
       </c>
       <c r="H127" t="n">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="I127" t="n">
-        <v>18.8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Recipe for Disaster/Defeating the Culinaromancer</t>
+          <t>Dream Mentor</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Desert Treasure I; Horror from the Deep; Recipe for Disaster/Freeing the Mountain Dwarf; Recipe for Disaster/Freeing the Goblin generals; Recipe for Disaster/Freeing Pirate Pete; Recipe for Disaster/Freeing the Lumbridge Guide; Recipe for Disaster/Freeing Evil Dave; Recipe for Disaster/Freeing Skrach Uglogwee; Recipe for Disaster/Freeing Sir Amik Varze; Recipe for Disaster/Freeing King Awowogei</t>
+          <t>Eadgar's Ruse; Lunar Diplomacy</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Quest point 175 (ID:23)</t>
+          <t>Combat 85 (ID:25)</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="I128" t="n">
-        <v>31.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Recruitment Drive</t>
+          <t>Grim Tales</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Black Knights' Fortress; Druidic Ritual</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>Druidic Ritual; Witch's House</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Agility 59 (ID:5); Farming 45 (ID:20); Herblore 52 (ID:8); Thieving 58 (ID:11); Woodcutting 71 (ID:18)</t>
+        </is>
+      </c>
       <c r="F129" t="n">
         <v>2</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Regicide</t>
+          <t>King's Ransom</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5124,67 +5024,75 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Underground Pass</t>
+          <t>Black Knights' Fortress; Holy Grail; Murder Mystery; One Small Favour</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Agility 56 (ID:5); Crafting 10 (ID:14)</t>
+          <t>Defence 65 (ID:7); Magic 45 (ID:16)</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G130" t="n">
         <v>2</v>
       </c>
       <c r="H130" t="n">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="I130" t="n">
-        <v>12.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>The Restless Ghost</t>
+          <t>Shilo Village</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Jungle Potion</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Agility 32 (ID:5); Crafting 20 (ID:14); Smithing 4 (ID:6)</t>
+        </is>
+      </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The Ribbiting Tale of a Lily Pad Labour Dispute</t>
+          <t>Biohazard</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5194,36 +5102,32 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Children of the Sun</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Woodcutting 15 (ID:18)</t>
-        </is>
-      </c>
+          <t>Plague City</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Romeo &amp; Juliet</t>
+          <t>Tower of Life</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5232,29 +5136,33 @@
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Construction 10 (ID:21)</t>
+        </is>
+      </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Roving Elves</t>
+          <t>Rag and Bone Man II</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5264,36 +5172,36 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Regicide; Waterfall Quest</t>
+          <t>The Fremennik Trials; Horror from the Deep; Rag and Bone Man I; Skippy and the Mogres; Started:Creature of Fenkenstrain; Started:Waterfall Quest; Started:Zogre Flesh Eaters</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Agility 56 (ID:5)</t>
+          <t>Defence 20 (ID:7); Slayer 40 (ID:19)</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I134" t="n">
-        <v>11.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Royal Trouble</t>
+          <t>Land of the Goblins</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5301,221 +5209,221 @@
           <t>Experienced</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Throne of Miscellania</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Agility 40 (ID:5); Slayer 40 (ID:19)</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Rum Deal</t>
+          <t>While Guthix Sleeps</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Grandmaster</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Priest in Peril; Zogre Flesh Eaters</t>
+          <t>Defender of Varrock; The Path of Glouphrie; Fight Arena; Dream Mentor; The Hand in the Sand; Wanted!; Temple of the Eye; Tears of Guthix; Nature Spirit; A Tail of Two Cats</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Crafting 42 (ID:14); Farming 40 (ID:20); Fishing 50 (ID:9); Prayer 47 (ID:13); Slayer 42 (ID:19)</t>
+          <t>Quest point 180 (ID:23); Thieving 72 (ID:11); Magic 67 (ID:16); Agility 66 (ID:5); Farming 65 (ID:20); Herblore 65 (ID:8); Hunter 62 (ID:22)</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G136" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H136" t="n">
-        <v>221</v>
+        <v>577</v>
       </c>
       <c r="I136" t="n">
-        <v>32.1</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Rune Mysteries</t>
+          <t>Zogre Flesh Eaters</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Big Chompy Bird Hunting; Jungle Potion</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Herblore 8 (ID:8); Ranged 30 (ID:10); Smithing 4 (ID:6)</t>
+        </is>
+      </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Scorpion Catcher</t>
+          <t>Monkey Madness II</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Grandmaster</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Alfred Grimhand's Barcrawl</t>
+          <t>Enlightened Journey; The Eyes of Glouphrie; Recipe for Disaster/Freeing King Awowogei; Troll Stronghold; Watchtower</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Prayer 31 (ID:13)</t>
+          <t>Agility 55 (ID:5); Crafting 70 (ID:14); Firemaking 60 (ID:15); Hunter 60 (ID:22); Slayer 69 (ID:19); Thieving 55 (ID:11)</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H138" t="n">
-        <v>31</v>
+        <v>369</v>
       </c>
       <c r="I138" t="n">
-        <v>7.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sea Slug</t>
+          <t>Client of Kourend</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Firemaking 30 (ID:15)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>X Marks the Spot</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Secrets of the North</t>
+          <t>The Queen of Thieves</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Making Friends with My Arm; The General's Shadow; Devious Minds; Hazeel Cult</t>
+          <t>Client of Kourend</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Agility 69 (ID:5); Thieving 64 (ID:11); Hunter 56 (ID:22)</t>
+          <t>Thieving 20 (ID:11)</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="I140" t="n">
-        <v>29.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Shades of Mort'ton</t>
+          <t>Bone Voyage</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5525,148 +5433,168 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Druidic Ritual; Priest in Peril</t>
+          <t>The Dig Site</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Crafting 20 (ID:14); Firemaking 5 (ID:15); Herblore 15 (ID:8)</t>
+          <t>Kudos 100 (ID:24)</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I141" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Shadow of the Storm</t>
+          <t>Dragon Slayer II</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Grandmaster</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Demon Slayer; The Golem</t>
+          <t>Animal Magnetism; Barbarian Firemaking; Bone Voyage; Client of Kourend; Dream Mentor; Ghosts Ahoy; Legends' Quest; A Tail of Two Cats</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Crafting 30 (ID:14)</t>
+          <t>Quest point 200 (ID:23); Agility 60 (ID:5); Construction 50 (ID:21); Crafting 62 (ID:14); Hitpoints 50 (ID:2); Magic 75 (ID:16); Mining 68 (ID:3); Smithing 70 (ID:6); Thieving 60 (ID:11)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H142" t="n">
-        <v>30</v>
+        <v>695</v>
       </c>
       <c r="I142" t="n">
-        <v>8</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Sheep Herder</t>
+          <t>The Depths of Despair</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Client of Kourend</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Agility 18 (ID:5)</t>
+        </is>
+      </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100.1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sheep Shearer</t>
+          <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Cook's Assistant</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Cooking 10 (ID:12)</t>
+        </is>
+      </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100.3</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Shield of Arrav</t>
+          <t>Recipe for Disaster/Freeing the Goblin generals</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Goblin Diplomacy; Recipe for Disaster/Another Cook's Quest</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -5675,318 +5603,326 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Shilo Village</t>
+          <t>Recipe for Disaster/Freeing the Mountain Dwarf</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Jungle Potion</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Agility 32 (ID:5); Crafting 20 (ID:14); Smithing 4 (ID:6)</t>
-        </is>
-      </c>
+          <t>Fishing Contest; Recipe for Disaster/Another Cook's Quest</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>11.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>100.6</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sins of the Father</t>
+          <t>Recipe for Disaster/Freeing Evil Dave</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>A Taste of Hope; Vampyre Slayer</t>
+          <t>Gertrude's Cat; Recipe for Disaster/Another Cook's Quest; Shadow of the Storm</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Agility 52 (ID:5); Attack 50 (ID:1); Crafting 56 (ID:14); Fletching 60 (ID:17); Magic 49 (ID:16); Slayer 50 (ID:19); Woodcutting 62 (ID:18)</t>
+          <t>Cooking 25 (ID:12)</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G147" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>379</v>
+        <v>25</v>
       </c>
       <c r="I147" t="n">
-        <v>50.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>The Slug Menace</t>
+          <t>Recipe for Disaster/Freeing Pirate Pete</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Sea Slug; Wanted!</t>
+          <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Crafting 30 (ID:14); Runecraft 30 (ID:18); Slayer 30 (ID:19); Thieving 30 (ID:11)</t>
+          <t>Cooking 31 (ID:12); Crafting 42 (ID:14); Smithing 31 (ID:6)</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H148" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="I148" t="n">
-        <v>20</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Song of the Elves</t>
+          <t>Recipe for Disaster/Freeing the Lumbridge Guide</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Grandmaster</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Druidic Ritual; Making History; Mourning's End Part II</t>
+          <t>Big Chompy Bird Hunting; Biohazard; Demon Slayer; Murder Mystery; Nature Spirit; Recipe for Disaster/Another Cook's Quest; Witch's House</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Agility 70 (ID:5); Construction 70 (ID:21); Farming 70 (ID:20); Herblore 70 (ID:8); Hunter 70 (ID:22); Mining 70 (ID:3); Smithing 70 (ID:6); Woodcutting 70 (ID:18)</t>
+          <t>Cooking 40 (ID:12)</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G149" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>560</v>
+        <v>40</v>
       </c>
       <c r="I149" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>100.8</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>A Soul's Bane</t>
+          <t>Recipe for Disaster/Freeing Sir Amik Varze</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Recipe for Disaster/Another Cook's Quest; Started:Legends' Quest</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Farming 20 (ID:20)</t>
+        </is>
+      </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Spirits of the Elid</t>
+          <t>Recipe for Disaster/Freeing King Awowogei</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Monkey Madness I; Recipe for Disaster/Another Cook's Quest</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Magic 33 (ID:16); Mining 37 (ID:3); Ranged 37 (ID:10); Thieving 37 (ID:11)</t>
+          <t>Agility 48 (ID:5); Cooking 70 (ID:12)</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H151" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="I151" t="n">
-        <v>20.4</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>100.9</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Swan Song</t>
+          <t>Recipe for Disaster/Freeing Skrach Uglogwee</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Garden of Tranquillity; One Small Favour</t>
+          <t>Big Chompy Bird Hunting; Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Quest point 100 (ID:23); Cooking 62 (ID:12); Crafting 40 (ID:14); Firemaking 42 (ID:15); Fishing 62 (ID:9); Magic 66 (ID:16); Smithing 45 (ID:6)</t>
+          <t>Cooking 41 (ID:12); Firemaking 20 (ID:15)</t>
         </is>
       </c>
       <c r="F152" t="n">
         <v>2</v>
       </c>
       <c r="G152" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H152" t="n">
-        <v>417</v>
+        <v>61</v>
       </c>
       <c r="I152" t="n">
-        <v>54.7</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tai Bwo Wannai Trio</t>
+          <t>A Taste of Hope</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Jungle Potion</t>
+          <t>Darkness of Hallowvale; Druidic Ritual</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Agility 15 (ID:5); Cooking 30 (ID:12); Fishing 5 (ID:9); Fishing 65 (ID:9); Herblore 34 (ID:8)</t>
+          <t>Agility 45 (ID:5); Attack 40 (ID:1); Crafting 48 (ID:14); Herblore 40 (ID:8); Slayer 38 (ID:19)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G153" t="n">
         <v>5</v>
       </c>
       <c r="H153" t="n">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="I153" t="n">
-        <v>22.9</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>A Tail of Two Cats</t>
+          <t>Tale of the Righteous</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5996,145 +5932,153 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Icthlarin's Little Helper</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>Client of Kourend</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Mining 10 (ID:3); Strength 16 (ID:4)</t>
+        </is>
+      </c>
       <c r="F154" t="n">
         <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I154" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tale of the Righteous</t>
+          <t>Making Friends with My Arm</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Client of Kourend</t>
+          <t>Cold War; My Arm's Big Adventure; Romeo &amp; Juliet; Swan Song</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mining 10 (ID:3); Strength 16 (ID:4)</t>
+          <t>Agility 68 (ID:5); Construction 35 (ID:21); Firemaking 66 (ID:15); Mining 72 (ID:3)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H155" t="n">
-        <v>26</v>
+        <v>241</v>
       </c>
       <c r="I155" t="n">
-        <v>7.6</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100.10</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>A Taste of Hope</t>
+          <t>Recipe for Disaster/Defeating the Culinaromancer</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Darkness of Hallowvale; Druidic Ritual</t>
+          <t>Desert Treasure I; Horror from the Deep; Recipe for Disaster/Freeing the Mountain Dwarf; Recipe for Disaster/Freeing the Goblin generals; Recipe for Disaster/Freeing Pirate Pete; Recipe for Disaster/Freeing the Lumbridge Guide; Recipe for Disaster/Freeing Evil Dave; Recipe for Disaster/Freeing Skrach Uglogwee; Recipe for Disaster/Freeing Sir Amik Varze; Recipe for Disaster/Freeing King Awowogei</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Agility 45 (ID:5); Attack 40 (ID:1); Crafting 48 (ID:14); Herblore 40 (ID:8); Slayer 38 (ID:19)</t>
+          <t>Quest point 175 (ID:23)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="I156" t="n">
-        <v>31.1</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tears of Guthix</t>
+          <t>Song of the Elves</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Grandmaster</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Druidic Ritual; Making History; Mourning's End Part II</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Quest point 43 (ID:23); Crafting 20 (ID:14); Firemaking 49 (ID:15); Mining 20 (ID:3)</t>
+          <t>Agility 70 (ID:5); Construction 70 (ID:21); Farming 70 (ID:20); Herblore 70 (ID:8); Hunter 70 (ID:22); Mining 70 (ID:3); Smithing 70 (ID:6); Woodcutting 70 (ID:18)</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G157" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H157" t="n">
-        <v>132</v>
+        <v>560</v>
       </c>
       <c r="I157" t="n">
-        <v>19.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Temple of Ikov</t>
+          <t>The Ascent of Arceuus</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6142,34 +6086,38 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Client of Kourend</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ranged 40 (ID:10); Thieving 42 (ID:11)</t>
+          <t>Hunter 12 (ID:22)</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="I158" t="n">
-        <v>12.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Temple of the Eye</t>
+          <t>The Forsaken Tower</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6179,246 +6127,258 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Enter the Abyss</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Runecraft 10 (ID:18)</t>
-        </is>
-      </c>
+          <t>Client of Kourend</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Throne of Miscellania</t>
+          <t>The Fremennik Exiles</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>The Fremennik Trials; Heroes' Quest</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>The Fremennik Isles; Lunar Diplomacy; Mountain Daughter; Heroes' Quest</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Crafting 65 (ID:14); Fishing 60 (ID:9); Runecraft 55 (ID:26); Slayer 60 (ID:19); Smithing 60 (ID:6)</t>
+        </is>
+      </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I160" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>The Tourist Trap</t>
+          <t>The Curse of Arrav</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Defender of Varrock; Troll Romance</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Fletching 10 (ID:17); Smithing 20 (ID:6)</t>
+          <t>Mining 64 (ID:3); Ranged 62 (ID:10); Thieving 62 (ID:11); Agility 61 (ID:5); Strength 58 (ID:4); Slayer 37 (ID:19)</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G161" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H161" t="n">
-        <v>30</v>
+        <v>344</v>
       </c>
       <c r="I161" t="n">
-        <v>7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Tower of Life</t>
+          <t>Defender of Varrock</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Novice</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Shield of Arrav; Temple of Ikov; Below Ice Mountain; Family Crest; Garden of Tranquillity; What Lies Below; Romeo &amp; Juliet; Demon Slayer</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Construction 10 (ID:21)</t>
+          <t>Smithing 55 (ID:6); Hunter 52 (ID:22)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" t="n">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="I162" t="n">
-        <v>3</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Tree Gnome Village</t>
+          <t>Sins of the Father</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>A Taste of Hope; Vampyre Slayer</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Agility 52 (ID:5); Attack 50 (ID:1); Crafting 56 (ID:14); Fletching 60 (ID:17); Magic 49 (ID:16); Slayer 50 (ID:19); Woodcutting 62 (ID:18)</t>
+        </is>
+      </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Tribal Totem</t>
+          <t>A Kingdom Divided</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Architectural Alliance; The Ascent of Arceuus; The Depths of Despair; Druidic Ritual; The Forsaken Tower; The Queen of Thieves; Tale of the Righteous</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Thieving 21 (ID:11)</t>
+          <t>Agility 54 (ID:5); Crafting 38 (ID:14); Herblore 50 (ID:8); Magic 35 (ID:16); Mining 42 (ID:3); Thieving 52 (ID:11); Woodcutting 52 (ID:18)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H164" t="n">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Troll Romance</t>
+          <t>A Porcine of Interest</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Troll Stronghold</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Agility 28 (ID:5); Woodcutting 45 (ID:18)</t>
-        </is>
-      </c>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>12.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Troll Stronghold</t>
+          <t>Getting Ahead</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6426,48 +6386,44 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Death Plateau</t>
-        </is>
-      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Agility 15 (ID:5)</t>
+          <t>Construction 26 (ID:21); Crafting 30 (ID:14)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H166" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="I166" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Twilight's Promise</t>
+          <t>A Night at the Theatre</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Children of the Sun</t>
+          <t>A Taste of Hope</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6481,57 +6437,49 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Underground Pass</t>
+          <t>Beneath Cursed Sands</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Biohazard</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Ranged 25 (ID:10)</t>
-        </is>
-      </c>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Vampyre Slayer</t>
+          <t>Temple of the Eye</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6539,69 +6487,77 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Enter the Abyss</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Runecraft 10 (ID:26)</t>
+        </is>
+      </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Wanted!</t>
+          <t>The Path of Glouphrie</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>The Lost Tribe; Priest in Peril; Recruitment Drive; Started:Enter the Abyss</t>
+          <t>The Eyes of Glouphrie; Waterfall Quest; Tree Gnome Village</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Quest point 32 (ID:23)</t>
+          <t>Strength 60 (ID:4); Slayer 56 (ID:19); Thieving 56 (ID:11); Ranged 47 (ID:10); Agility 45 (ID:5)</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G170" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H170" t="n">
-        <v>32</v>
+        <v>264</v>
       </c>
       <c r="I170" t="n">
-        <v>10.2</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Watchtower</t>
+          <t>Sleeping Giants</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6609,38 +6565,30 @@
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Druidic Ritual</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Agility 25 (ID:5); Herblore 14 (ID:8); Magic 15 (ID:16); Mining 40 (ID:3); Thieving 15 (ID:11)</t>
-        </is>
-      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>18.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Waterfall Quest</t>
+          <t>The Garden of Death</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6649,107 +6597,111 @@
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Farming 20 (ID:20)</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>What Lies Below</t>
+          <t>Desert Treasure II - The Fallen Empire</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Grandmaster</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Rune Mysteries</t>
+          <t>Desert Treasure I; Secrets of the North; Enakhra's Lament; Temple of the Eye; The Garden of Death; Below Ice Mountain; His Faithful Servants</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Runecraft 35 (ID:18)</t>
+          <t>Firemaking 75 (ID:15); Magic 75 (ID:16); Herblore 62 (ID:8); Thieving 70 (ID:11); Runecraft 60 (ID:26); Construction 60 (ID:21)</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H173" t="n">
-        <v>35</v>
+        <v>402</v>
       </c>
       <c r="I173" t="n">
-        <v>7.5</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>While Guthix Sleeps</t>
+          <t>Secrets of the North</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Grandmaster</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Defender of Varrock; The Path of Glouphrie; Fight Arena; Dream Mentor; The Hand in the Sand; Wanted!; Temple of the Eye; Tears of Guthix; Nature Spirit; A Tail of Two Cats</t>
+          <t>Making Friends with My Arm; The General's Shadow; Devious Minds; Hazeel Cult</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Quest point 180 (ID:23); Thieving 72 (ID:11); Magic 67 (ID:16); Agility 66 (ID:5); Farming 65 (ID:20); Herblore 65 (ID:8); Hunter 62 (ID:22)</t>
+          <t>Agility 69 (ID:5); Thieving 64 (ID:11); Hunter 56 (ID:22)</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G174" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H174" t="n">
-        <v>577</v>
+        <v>189</v>
       </c>
       <c r="I174" t="n">
-        <v>79.7</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Witch's Potion</t>
+          <t>Children of the Sun</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6775,43 +6727,51 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Witch's House</t>
+          <t>Perilous Moons</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Twilight's Promise</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Slayer 48 (ID:19); Hunter 20 (ID:22); Fishing 20 (ID:9); Runecraft 20 (ID:26); Construction 10 (ID:21)</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H176" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>X Marks the Spot</t>
+          <t>The Ribbiting Tale of a Lily Pad Labour Dispute</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6819,30 +6779,38 @@
           <t>Novice</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Children of the Sun</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Woodcutting 15 (ID:18)</t>
+        </is>
+      </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Zogre Flesh Eaters</t>
+          <t>Twilight's Promise</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6852,25 +6820,429 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Big Chompy Bird Hunting; Jungle Potion</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Herblore 8 (ID:8); Ranged 30 (ID:10); Smithing 4 (ID:6)</t>
-        </is>
-      </c>
+          <t>Children of the Sun</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
         <v>3</v>
       </c>
-      <c r="H178" t="n">
-        <v>42</v>
-      </c>
-      <c r="I178" t="n">
-        <v>11.2</v>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>At First Light</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Children of the Sun; Eagles' Peak</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Hunter 46 (ID:22); Herblore 30 (ID:8); Construction 27 (ID:21)</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" t="n">
+        <v>103</v>
+      </c>
+      <c r="I179" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>The Heart of Darkness</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Twilight's Promise</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Mining 55 (ID:3); Thieving 48 (ID:11); Slayer 48 (ID:19); Agility 46 (ID:5)</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" t="n">
+        <v>4</v>
+      </c>
+      <c r="H180" t="n">
+        <v>197</v>
+      </c>
+      <c r="I180" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Death on the Isle</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Children of the Sun</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Agility 32 (ID:5); Thieving 34 (ID:11)</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" t="n">
+        <v>2</v>
+      </c>
+      <c r="H181" t="n">
+        <v>66</v>
+      </c>
+      <c r="I181" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Meat and Greet</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Children of the Sun</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ethically Acquired Antiquities</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Children of the Sun; Shield of Arrav</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Thieving 25 (ID:11)</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>2</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>25</v>
+      </c>
+      <c r="I183" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>The Final Dawn</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pandemonium</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Prying Times</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Current Affairs</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Troubled Tortugans</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Shadows of Custodia</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Scrambled!</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Data/quest_reference.xlsx
+++ b/Data/quest_reference.xlsx
@@ -475,10 +475,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
+      <c r="A2" t="n">
+        <v>188</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -506,10 +504,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -537,10 +533,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="A4" t="n">
+        <v>158</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -572,10 +566,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="A5" t="n">
+        <v>152</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -603,10 +595,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
+      <c r="A6" t="n">
+        <v>145</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -634,10 +624,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+      <c r="A7" t="n">
+        <v>139</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -665,10 +653,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A8" t="n">
+        <v>51</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -696,10 +682,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A9" t="n">
+        <v>17</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -731,10 +715,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A10" t="n">
+        <v>16</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -762,10 +744,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A11" t="n">
+        <v>15</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -793,10 +773,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A12" t="n">
+        <v>14</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -828,10 +806,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A13" t="n">
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -859,10 +835,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A14" t="n">
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -894,10 +868,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A15" t="n">
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -929,10 +901,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A16" t="n">
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -960,10 +930,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A17" t="n">
+        <v>9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -991,10 +959,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A18" t="n">
+        <v>8</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1022,10 +988,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A19" t="n">
+        <v>7</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1053,10 +1017,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A20" t="n">
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1084,10 +1046,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A21" t="n">
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1115,10 +1075,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A22" t="n">
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1146,10 +1104,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A23" t="n">
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1177,10 +1133,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A24" t="n">
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1208,10 +1162,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A25" t="n">
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1239,10 +1191,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A26" t="n">
+        <v>18</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1270,10 +1220,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A27" t="n">
+        <v>19</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1305,10 +1253,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A28" t="n">
+        <v>20</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1336,10 +1282,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A29" t="n">
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1367,10 +1311,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A30" t="n">
+        <v>22</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1406,10 +1348,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A31" t="n">
+        <v>23</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1445,10 +1385,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A32" t="n">
+        <v>24</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1480,10 +1418,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A33" t="n">
+        <v>26</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1515,10 +1451,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A34" t="n">
+        <v>25</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1550,10 +1484,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A35" t="n">
+        <v>27</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1581,10 +1513,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A36" t="n">
+        <v>28</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1616,10 +1546,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A37" t="n">
+        <v>29</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1647,10 +1575,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A38" t="n">
+        <v>30</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1686,10 +1612,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A39" t="n">
+        <v>31</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1717,10 +1641,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="A40" t="n">
+        <v>32</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1748,10 +1670,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A41" t="n">
+        <v>33</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1779,10 +1699,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A42" t="n">
+        <v>34</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1810,10 +1728,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A43" t="n">
+        <v>35</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1841,10 +1757,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="A44" t="n">
+        <v>36</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1876,10 +1790,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A45" t="n">
+        <v>37</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1907,10 +1819,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A46" t="n">
+        <v>39</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1946,10 +1856,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A47" t="n">
+        <v>40</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1981,10 +1889,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A48" t="n">
+        <v>42</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2020,10 +1926,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="A49" t="n">
+        <v>43</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2051,10 +1955,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="A50" t="n">
+        <v>44</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2086,10 +1988,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="A51" t="n">
+        <v>45</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2125,10 +2025,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="A52" t="n">
+        <v>46</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2156,10 +2054,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="A53" t="n">
+        <v>47</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2187,10 +2083,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A54" t="n">
+        <v>48</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2226,10 +2120,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="A55" t="n">
+        <v>49</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2257,10 +2149,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="A56" t="n">
+        <v>50</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2296,10 +2186,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="A57" t="n">
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2327,10 +2215,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A58" t="n">
+        <v>60</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2366,10 +2252,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A59" t="n">
+        <v>52</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2401,10 +2285,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="A60" t="n">
+        <v>53</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2436,10 +2318,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A61" t="n">
+        <v>55</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2475,10 +2355,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A62" t="n">
+        <v>54</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2506,10 +2384,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="A63" t="n">
+        <v>59</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2545,10 +2421,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="A64" t="n">
+        <v>58</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2584,10 +2458,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A65" t="n">
+        <v>57</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2623,10 +2495,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="A66" t="n">
+        <v>61</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2662,10 +2532,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A67" t="n">
+        <v>62</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2693,10 +2561,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="A68" t="n">
+        <v>63</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2732,10 +2598,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="A69" t="n">
+        <v>64</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2767,10 +2631,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="A70" t="n">
+        <v>65</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2802,10 +2664,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="A71" t="n">
+        <v>66</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2841,10 +2701,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="A72" t="n">
+        <v>67</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2880,10 +2738,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="A73" t="n">
+        <v>68</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2919,10 +2775,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="A74" t="n">
+        <v>69</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2958,10 +2812,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="A75" t="n">
+        <v>70</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2997,10 +2849,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="A76" t="n">
+        <v>71</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3036,10 +2886,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="A77" t="n">
+        <v>72</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3075,10 +2923,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="A78" t="n">
+        <v>73</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3110,10 +2956,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="A79" t="n">
+        <v>74</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3149,10 +2993,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="A80" t="n">
+        <v>75</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3184,10 +3026,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="A81" t="n">
+        <v>76</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3219,10 +3059,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A82" t="n">
+        <v>77</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3258,10 +3096,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A83" t="n">
+        <v>78</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3293,10 +3129,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="A84" t="n">
+        <v>79</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3328,10 +3162,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="A85" t="n">
+        <v>81</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3367,10 +3199,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A86" t="n">
+        <v>82</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3402,10 +3232,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="A87" t="n">
+        <v>83</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3437,10 +3265,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="A88" t="n">
+        <v>84</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3476,10 +3302,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="A89" t="n">
+        <v>85</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3515,10 +3339,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="A90" t="n">
+        <v>86</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3554,10 +3376,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="A91" t="n">
+        <v>87</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3589,10 +3409,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="A92" t="n">
+        <v>88</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3628,10 +3446,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="A93" t="n">
+        <v>89</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3663,10 +3479,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="A94" t="n">
+        <v>90</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3702,10 +3516,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="A95" t="n">
+        <v>91</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3741,10 +3553,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="A96" t="n">
+        <v>92</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3776,10 +3586,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="A97" t="n">
+        <v>93</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3811,10 +3619,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+      <c r="A98" t="n">
+        <v>94</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3846,10 +3652,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="A99" t="n">
+        <v>95</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3885,10 +3689,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="A100" t="n">
+        <v>96</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3920,10 +3722,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="A101" t="n">
+        <v>97</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3955,10 +3755,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="A102" t="n">
+        <v>98</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3994,10 +3792,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="A103" t="n">
+        <v>99</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -4029,10 +3825,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="A104" t="n">
+        <v>100</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -4064,10 +3858,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="A105" t="n">
+        <v>111</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -4103,10 +3895,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
+      <c r="A106" t="n">
+        <v>112</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -4134,10 +3924,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="A107" t="n">
+        <v>113</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -4165,10 +3953,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="A108" t="n">
+        <v>114</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4204,10 +3990,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="A109" t="n">
+        <v>115</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4243,10 +4027,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="A110" t="n">
+        <v>116</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4282,10 +4064,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="A111" t="n">
+        <v>117</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -4321,10 +4101,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="A112" t="n">
+        <v>118</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4360,10 +4138,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A113" t="n">
+        <v>119</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4399,10 +4175,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="A114" t="n">
+        <v>120</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4438,10 +4212,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="A115" t="n">
+        <v>121</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -4477,10 +4249,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="A116" t="n">
+        <v>122</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4516,10 +4286,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="A117" t="n">
+        <v>123</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -4555,10 +4323,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="A118" t="n">
+        <v>124</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -4590,10 +4356,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="A119" t="n">
+        <v>125</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -4625,10 +4389,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="A120" t="n">
+        <v>126</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -4664,10 +4426,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="A121" t="n">
+        <v>127</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -4699,10 +4459,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="A122" t="n">
+        <v>128</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -4734,10 +4492,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="A123" t="n">
+        <v>129</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -4773,10 +4529,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="A124" t="n">
+        <v>131</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -4812,10 +4566,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="A125" t="n">
+        <v>132</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -4851,10 +4603,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="A126" t="n">
+        <v>133</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -4890,10 +4640,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="A127" t="n">
+        <v>134</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -4929,10 +4677,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="A128" t="n">
+        <v>135</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -4968,10 +4714,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="A129" t="n">
+        <v>136</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -5007,10 +4751,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="A130" t="n">
+        <v>137</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -5046,10 +4788,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A131" t="n">
+        <v>41</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -5085,10 +4825,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A132" t="n">
+        <v>38</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -5120,10 +4858,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="A133" t="n">
+        <v>130</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -5155,10 +4891,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="A134" t="n">
+        <v>141</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -5194,10 +4928,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+      <c r="A135" t="n">
+        <v>161</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -5225,10 +4957,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="A136" t="n">
+        <v>175</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -5264,10 +4994,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="A137" t="n">
+        <v>80</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -5303,10 +5031,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="A138" t="n">
+        <v>138</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -5342,10 +5068,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A139" t="n">
+        <v>140</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5377,10 +5101,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="A140" t="n">
+        <v>143</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -5416,10 +5138,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="A141" t="n">
+        <v>142</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -5455,10 +5175,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="A142" t="n">
+        <v>146</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -5494,10 +5212,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="A143" t="n">
+        <v>144</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -5533,10 +5249,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A144" t="n">
+        <v>101</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -5572,10 +5286,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>100.3</t>
-        </is>
+      <c r="A145" t="n">
+        <v>103</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -5607,10 +5319,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>100.2</t>
-        </is>
+      <c r="A146" t="n">
+        <v>102</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -5642,10 +5352,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
+      <c r="A147" t="n">
+        <v>106</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -5681,10 +5389,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>100.4</t>
-        </is>
+      <c r="A148" t="n">
+        <v>104</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -5720,10 +5426,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="A149" t="n">
+        <v>105</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -5759,10 +5463,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>100.8</t>
-        </is>
+      <c r="A150" t="n">
+        <v>108</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -5798,10 +5500,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>100.7</t>
-        </is>
+      <c r="A151" t="n">
+        <v>107</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -5837,10 +5537,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
+      <c r="A152" t="n">
+        <v>109</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -5876,10 +5574,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="A153" t="n">
+        <v>148</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -5915,10 +5611,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="A154" t="n">
+        <v>147</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -5954,10 +5648,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="A155" t="n">
+        <v>149</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -5993,10 +5685,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="A156" t="n">
+        <v>110</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -6032,10 +5722,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="A157" t="n">
+        <v>153</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -6071,10 +5759,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="A158" t="n">
+        <v>151</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -6110,10 +5796,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
+      <c r="A159" t="n">
+        <v>150</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -6145,10 +5829,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="A160" t="n">
+        <v>154</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -6184,10 +5866,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="A161" t="n">
+        <v>180</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -6223,10 +5903,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A162" t="n">
+        <v>170</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -6262,10 +5940,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+      <c r="A163" t="n">
+        <v>155</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -6301,10 +5977,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="A164" t="n">
+        <v>160</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -6340,10 +6014,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="A165" t="n">
+        <v>156</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -6371,10 +6043,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
+      <c r="A166" t="n">
+        <v>157</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -6406,10 +6076,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="A167" t="n">
+        <v>159</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -6441,10 +6109,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
+      <c r="A168" t="n">
+        <v>163</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -6472,10 +6138,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="A169" t="n">
+        <v>162</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -6511,10 +6175,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="A170" t="n">
+        <v>168</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -6550,10 +6212,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
+      <c r="A171" t="n">
+        <v>164</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -6581,10 +6241,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+      <c r="A172" t="n">
+        <v>165</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -6616,10 +6274,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="A173" t="n">
+        <v>167</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -6655,10 +6311,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="A174" t="n">
+        <v>166</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -6694,10 +6348,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A175" t="n">
+        <v>169</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -6725,10 +6377,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="A176" t="n">
+        <v>173</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -6764,10 +6414,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
+      <c r="A177" t="n">
+        <v>174</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -6803,10 +6451,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="A178" t="n">
+        <v>171</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -6838,10 +6484,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+      <c r="A179" t="n">
+        <v>172</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -6877,10 +6521,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
+      <c r="A180" t="n">
+        <v>176</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -6916,10 +6558,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="A181" t="n">
+        <v>177</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -6955,10 +6595,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+      <c r="A182" t="n">
+        <v>178</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -6990,10 +6628,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+      <c r="A183" t="n">
+        <v>179</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -7029,10 +6665,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
+      <c r="A184" t="n">
+        <v>181</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -7060,10 +6694,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
+      <c r="A185" t="n">
+        <v>184</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -7091,10 +6723,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
+      <c r="A186" t="n">
+        <v>185</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -7122,10 +6752,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+      <c r="A187" t="n">
+        <v>186</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -7153,10 +6781,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
+      <c r="A188" t="n">
+        <v>187</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -7184,10 +6810,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
+      <c r="A189" t="n">
+        <v>182</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -7215,10 +6839,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="A190" t="n">
+        <v>183</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
